--- a/気分（きぶん）.xlsx
+++ b/気分（きぶん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="恋人の気持ち" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="540">
   <si>
     <t>曖昧</t>
   </si>
@@ -1503,6 +1503,35 @@
     <t>かつりょく</t>
   </si>
   <si>
+    <t>心使い</t>
+  </si>
+  <si>
+    <t>こころつかい</t>
+  </si>
+  <si>
+    <r>
+      <t>对</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>别人的体</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>贴与关照</t>
+    </r>
+  </si>
+  <si>
     <t>思い過ごし</t>
   </si>
   <si>
@@ -1639,6 +1668,12 @@
   </si>
   <si>
     <t>おろか</t>
+  </si>
+  <si>
+    <t>倹約</t>
+  </si>
+  <si>
+    <t>けんやく</t>
   </si>
   <si>
     <r>
@@ -1874,7 +1909,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1928,15 +1963,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="宋体"/>
+      <charset val="128"/>
     </font>
     <font>
       <u/>
@@ -2080,13 +2108,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2393,28 +2414,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2423,118 +2447,115 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4247,7 +4268,7 @@
       <c r="B38" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="5" t="s">
         <v>352</v>
       </c>
     </row>
@@ -4258,7 +4279,7 @@
       <c r="B39" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="5" t="s">
         <v>355</v>
       </c>
     </row>
@@ -4309,7 +4330,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G37"/>
+  <dimension ref="A2:G38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" style="2" customWidth="1"/>
@@ -4594,7 +4615,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
         <v>428</v>
       </c>
@@ -4602,7 +4623,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
         <v>430</v>
       </c>
@@ -4610,7 +4631,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
         <v>432</v>
       </c>
@@ -4618,7 +4639,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
         <v>434</v>
       </c>
@@ -4626,12 +4647,23 @@
         <v>435</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
         <v>436</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>437</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -4643,7 +4675,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G16"/>
+  <dimension ref="A2:G17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -4653,30 +4685,30 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>117</v>
@@ -4687,10 +4719,10 @@
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>129</v>
@@ -4701,134 +4733,142 @@
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>487</v>
+      </c>
+      <c r="B17" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -4852,202 +4892,202 @@
   <sheetData>
     <row r="2" ht="18" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="2" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="2" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B6" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="2" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="2" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="10" ht="15.6" spans="1:16">
       <c r="A10" s="4" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C10" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:16">
       <c r="A11" s="4" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="A12" s="2" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="P14" s="6"/>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B16" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>

--- a/気分（きぶん）.xlsx
+++ b/気分（きぶん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="恋人の気持ち" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="550">
   <si>
     <t>曖昧</t>
   </si>
@@ -265,10 +265,25 @@
     <t>げきじょう</t>
   </si>
   <si>
+    <t>友好</t>
+  </si>
+  <si>
+    <t>ゆうこう</t>
+  </si>
+  <si>
     <t>刺激</t>
   </si>
   <si>
     <t>しげき</t>
+  </si>
+  <si>
+    <t>安らか</t>
+  </si>
+  <si>
+    <t>やすらか</t>
+  </si>
+  <si>
+    <t>（安乐，安定）</t>
   </si>
   <si>
     <t>充実感</t>
@@ -382,9 +397,6 @@
     <t>むてき</t>
   </si>
   <si>
-    <t>無邪気</t>
-  </si>
-  <si>
     <t>むじゃき</t>
   </si>
   <si>
@@ -731,6 +743,15 @@
   </si>
   <si>
     <t>ひとりごと</t>
+  </si>
+  <si>
+    <t>躊躇い</t>
+  </si>
+  <si>
+    <t>ためらい</t>
+  </si>
+  <si>
+    <t>踌躇的</t>
   </si>
   <si>
     <t>自暴自棄</t>
@@ -1345,12 +1366,6 @@
     <t>じしんまんまん</t>
   </si>
   <si>
-    <t>友好</t>
-  </si>
-  <si>
-    <t>ゆうこう</t>
-  </si>
-  <si>
     <t>活躍</t>
   </si>
   <si>
@@ -1510,6 +1525,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
       <t>对</t>
     </r>
     <r>
@@ -1676,6 +1697,15 @@
     <t>けんやく</t>
   </si>
   <si>
+    <t>用心深い</t>
+  </si>
+  <si>
+    <t>ようじんぶかい</t>
+  </si>
+  <si>
+    <t>（小心谨慎）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1897,6 +1927,12 @@
   </si>
   <si>
     <t>ひきょう</t>
+  </si>
+  <si>
+    <t>逃避</t>
+  </si>
+  <si>
+    <t>とうひ</t>
   </si>
 </sst>
 </file>
@@ -3171,46 +3207,61 @@
       <c r="B16" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="17" ht="18" spans="1:3">
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" ht="18" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" ht="18" spans="1:3">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" ht="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" ht="18" spans="1:3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" ht="18" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" ht="18" spans="1:3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" ht="18" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" ht="18" spans="1:3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" ht="18" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>45</v>
       </c>
@@ -3218,91 +3269,88 @@
         <v>46</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" ht="18" spans="1:3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" ht="18" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" ht="18" spans="1:3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" ht="18" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" ht="18" spans="1:3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" ht="18" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" ht="18" spans="1:3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" ht="18" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" ht="18" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" ht="18" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" ht="18" spans="1:3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" ht="18" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" ht="18" spans="1:3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" ht="18" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" ht="18" spans="1:3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" ht="18" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>105</v>
-      </c>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="B30" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3314,7 +3362,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G39"/>
+  <dimension ref="A2:G40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
@@ -3326,413 +3374,424 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G10" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C17" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C19" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C20" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C24" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C25" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C28" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C31" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C37" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C38" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B39" t="s">
-        <v>215</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>220</v>
+      </c>
+      <c r="B40" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3755,570 +3814,570 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G16" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:7">
       <c r="A20" s="2" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:7">
       <c r="A21" s="2" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:7">
       <c r="A23" s="2" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C23" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:7">
       <c r="A25" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:7">
       <c r="A26" s="2" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C26" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E27" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F27" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:7">
       <c r="A28" s="2" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C28" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E28" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F28" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:7">
       <c r="A29" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:7">
       <c r="A30" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="31" ht="15.6" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C31" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:7">
       <c r="A32" s="2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C32" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C33" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:5">
       <c r="B34" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C34" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C35" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C36" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -4339,114 +4398,114 @@
   <sheetData>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4459,117 +4518,117 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>394</v>
+        <v>75</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>395</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -4582,88 +4641,88 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -4675,7 +4734,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G17"/>
+  <dimension ref="A2:G18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -4685,190 +4744,201 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C3" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B17" t="s">
-        <v>488</v>
+        <v>493</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>494</v>
+      </c>
+      <c r="B18" t="s">
+        <v>495</v>
+      </c>
+      <c r="C18" t="s">
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -4880,7 +4950,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:P21"/>
+  <dimension ref="A2:P22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -4892,202 +4962,210 @@
   <sheetData>
     <row r="2" ht="18" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="2" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" s="2" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="2" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B6" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="2" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="2" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B8" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="2" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="10" ht="15.6" spans="1:16">
       <c r="A10" s="4" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C10" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:16">
       <c r="A11" s="4" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="A12" s="2" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="P14" s="6"/>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B16" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>539</v>
+        <v>547</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>548</v>
+      </c>
+      <c r="B22" t="s">
+        <v>549</v>
       </c>
     </row>
   </sheetData>

--- a/気分（きぶん）.xlsx
+++ b/気分（きぶん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="5"/>
+    <workbookView windowWidth="18288" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="恋人の気持ち" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="556">
   <si>
     <t>曖昧</t>
   </si>
@@ -752,6 +752,12 @@
   </si>
   <si>
     <t>踌躇的</t>
+  </si>
+  <si>
+    <t>反省</t>
+  </si>
+  <si>
+    <t>はんせい</t>
   </si>
   <si>
     <t>自暴自棄</t>
@@ -1113,6 +1119,12 @@
     <t>くつう</t>
   </si>
   <si>
+    <t>悪罵</t>
+  </si>
+  <si>
+    <t>あくば</t>
+  </si>
+  <si>
     <t>退廃</t>
   </si>
   <si>
@@ -1459,6 +1471,12 @@
   </si>
   <si>
     <t>かっこたるいし</t>
+  </si>
+  <si>
+    <t>自由意志</t>
+  </si>
+  <si>
+    <t>じゆういし</t>
   </si>
   <si>
     <t>真面目</t>
@@ -3362,7 +3380,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G40"/>
+  <dimension ref="A2:G41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
@@ -3792,6 +3810,14 @@
       </c>
       <c r="C40" t="s">
         <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -3814,96 +3840,96 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
@@ -3914,198 +3940,198 @@
         <v>158</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G16" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:7">
       <c r="A20" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:7">
       <c r="A21" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>186</v>
@@ -4114,270 +4140,276 @@
         <v>187</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:7">
       <c r="A23" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C23" t="s">
+        <v>313</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C23" t="s">
-        <v>311</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:7">
       <c r="A25" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:7">
       <c r="A26" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C26" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E27" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F27" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:7">
       <c r="A28" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C28" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E28" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F28" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:7">
       <c r="A29" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
+      </c>
+      <c r="E29" t="s">
+        <v>336</v>
+      </c>
+      <c r="F29" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:7">
       <c r="A30" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" ht="15.6" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C31" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:7">
       <c r="A32" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C32" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C33" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:5">
       <c r="B34" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C34" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C35" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C36" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -4389,7 +4421,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G38"/>
+  <dimension ref="A2:G39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" style="2" customWidth="1"/>
@@ -4398,114 +4430,114 @@
   <sheetData>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4526,203 +4558,211 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>428</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>44</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>424</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>425</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -4744,30 +4784,30 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C3" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>121</v>
@@ -4778,10 +4818,10 @@
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>133</v>
@@ -4792,153 +4832,153 @@
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B17" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B18" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="C18" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -4962,210 +5002,210 @@
   <sheetData>
     <row r="2" ht="18" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="2" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" s="2" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B6" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="2" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B8" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" ht="15.6" spans="1:16">
       <c r="A10" s="4" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C10" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:16">
       <c r="A11" s="4" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="A12" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="P14" s="6"/>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B16" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B22" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/気分（きぶん）.xlsx
+++ b/気分（きぶん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18288" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="恋人の気持ち" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="558">
   <si>
     <t>曖昧</t>
   </si>
@@ -293,6 +293,12 @@
   </si>
   <si>
     <t>（很活跃，很积极）</t>
+  </si>
+  <si>
+    <t>幸運</t>
+  </si>
+  <si>
+    <t>こううん</t>
   </si>
   <si>
     <t>大活躍</t>
@@ -3259,24 +3265,30 @@
       <c r="C18" t="s">
         <v>84</v>
       </c>
+      <c r="D18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="19" ht="18" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:6">
@@ -3287,88 +3299,88 @@
         <v>46</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -3392,296 +3404,296 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C22" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
@@ -3694,130 +3706,130 @@
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C31" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C34" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B37" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C37" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B38" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B39" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C40" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B41" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -3840,576 +3852,576 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G16" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C17" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:7">
       <c r="A20" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:7">
       <c r="A21" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:7">
       <c r="A23" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" t="s">
+        <v>315</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C23" t="s">
-        <v>313</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:7">
       <c r="A25" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:7">
       <c r="A26" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C26" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E27" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F27" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:7">
       <c r="A28" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C28" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F28" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:7">
       <c r="A29" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E29" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F29" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:7">
       <c r="A30" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" ht="15.6" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C31" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:7">
       <c r="A32" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C32" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C33" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:5">
       <c r="B34" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C34" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C35" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C36" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4430,114 +4442,114 @@
   <sheetData>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4558,117 +4570,117 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4681,88 +4693,88 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -4784,201 +4796,201 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B17" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B18" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C18" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -5002,210 +5014,210 @@
   <sheetData>
     <row r="2" ht="18" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B6" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B8" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" ht="15.6" spans="1:16">
       <c r="A10" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C10" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:16">
       <c r="A11" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="A12" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="P14" s="6"/>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B16" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B22" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>

--- a/気分（きぶん）.xlsx
+++ b/気分（きぶん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="恋人の気持ち" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="569">
   <si>
     <t>曖昧</t>
   </si>
@@ -1137,6 +1137,15 @@
     <t>たいはい</t>
   </si>
   <si>
+    <t>前非</t>
+  </si>
+  <si>
+    <t>ぜんぴ</t>
+  </si>
+  <si>
+    <t>前非を悔いる｜痛改前非</t>
+  </si>
+  <si>
     <t>溜息</t>
   </si>
   <si>
@@ -1730,6 +1739,15 @@
     <t>（小心谨慎）</t>
   </si>
   <si>
+    <t>強情</t>
+  </si>
+  <si>
+    <t>ごうじょう</t>
+  </si>
+  <si>
+    <t>（固执）＝かたまり</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1845,10 +1863,25 @@
     <t>ぶべつ</t>
   </si>
   <si>
+    <t>塊り</t>
+  </si>
+  <si>
+    <t>かたまり</t>
+  </si>
+  <si>
+    <t>（固执的人）</t>
+  </si>
+  <si>
     <t>軽蔑</t>
   </si>
   <si>
     <t>けいめつ</t>
+  </si>
+  <si>
+    <t>軽視</t>
+  </si>
+  <si>
+    <t>けいし</t>
   </si>
   <si>
     <t>邪悪</t>
@@ -2005,13 +2038,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Segoe UI Symbol"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4283,145 +4316,154 @@
       <c r="B30" s="2" t="s">
         <v>341</v>
       </c>
+      <c r="E30" t="s">
+        <v>342</v>
+      </c>
+      <c r="F30" t="s">
+        <v>343</v>
+      </c>
+      <c r="G30" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="31" ht="15.6" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C31" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:7">
       <c r="A32" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C32" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C33" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:5">
       <c r="B34" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C34" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C35" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C36" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4442,114 +4484,114 @@
   <sheetData>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4570,117 +4612,117 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4693,88 +4735,88 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -4786,7 +4828,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G18"/>
+  <dimension ref="A2:G19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -4796,30 +4838,30 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C3" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>123</v>
@@ -4830,10 +4872,10 @@
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>135</v>
@@ -4844,153 +4886,164 @@
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B17" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B18" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C18" t="s">
-        <v>504</v>
+        <v>507</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>508</v>
+      </c>
+      <c r="B19" t="s">
+        <v>509</v>
+      </c>
+      <c r="C19" t="s">
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -5002,7 +5055,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:P22"/>
+  <dimension ref="A2:P23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -5014,210 +5067,227 @@
   <sheetData>
     <row r="2" ht="18" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="2" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" s="2" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="2" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B6" t="s">
-        <v>525</v>
+        <v>531</v>
+      </c>
+      <c r="E6" t="s">
+        <v>532</v>
+      </c>
+      <c r="F6" t="s">
+        <v>533</v>
+      </c>
+      <c r="G6" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="2" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="8" ht="18" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>528</v>
+        <v>536</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>537</v>
       </c>
       <c r="B8" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="10" ht="15.6" spans="1:16">
-      <c r="A10" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="C10" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="11" ht="18" spans="1:16">
+        <v>539</v>
+      </c>
+      <c r="B9" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="10" ht="18" spans="1:16">
+      <c r="A10" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="11" ht="15.6" spans="1:16">
       <c r="A11" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>536</v>
+        <v>543</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="C11" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
-      <c r="A12" s="2" t="s">
-        <v>537</v>
+      <c r="A12" s="4" t="s">
+        <v>546</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="P14" s="6"/>
+        <v>550</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="P14" s="5"/>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>544</v>
+        <v>552</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="B16" t="s">
-        <v>546</v>
+        <v>554</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>548</v>
+        <v>556</v>
+      </c>
+      <c r="B17" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>556</v>
-      </c>
-      <c r="B22" t="s">
-        <v>557</v>
+        <v>563</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="22" ht="18" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>567</v>
+      </c>
+      <c r="B23" t="s">
+        <v>568</v>
       </c>
     </row>
   </sheetData>

--- a/気分（きぶん）.xlsx
+++ b/気分（きぶん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="5"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="恋人の気持ち" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="573">
   <si>
     <t>曖昧</t>
   </si>
@@ -548,6 +548,9 @@
   </si>
   <si>
     <t>ぎわく</t>
+  </si>
+  <si>
+    <t>疑惑を生む</t>
   </si>
   <si>
     <t>疑問</t>
@@ -1746,6 +1749,15 @@
   </si>
   <si>
     <t>（固执）＝かたまり</t>
+  </si>
+  <si>
+    <t>省エネ</t>
+  </si>
+  <si>
+    <t>しょうえね</t>
+  </si>
+  <si>
+    <t>（省电、佛系）</t>
   </si>
   <si>
     <r>
@@ -3599,134 +3611,137 @@
       <c r="B13" s="2" t="s">
         <v>160</v>
       </c>
+      <c r="C13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
@@ -3739,13 +3754,13 @@
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
@@ -3756,113 +3771,113 @@
         <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B37" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C37" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B40" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -3885,96 +3900,96 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
@@ -3985,485 +4000,485 @@
         <v>160</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:7">
       <c r="A20" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:7">
       <c r="A21" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:7">
       <c r="A23" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C23" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:7">
       <c r="A25" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:7">
       <c r="A26" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C26" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E27" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F27" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:7">
       <c r="A28" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C28" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E28" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F28" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:7">
       <c r="A29" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E29" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:7">
       <c r="A30" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E30" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G30" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" ht="15.6" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C31" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:7">
       <c r="A32" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C32" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C33" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:5">
       <c r="B34" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C34" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C35" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C36" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4484,114 +4499,114 @@
   <sheetData>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4612,117 +4627,117 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4735,88 +4750,88 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -4828,7 +4843,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G19"/>
+  <dimension ref="A2:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -4838,30 +4853,30 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>123</v>
@@ -4872,10 +4887,10 @@
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>135</v>
@@ -4886,164 +4901,175 @@
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B17" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B18" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C18" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B19" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C19" t="s">
-        <v>510</v>
+        <v>511</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>512</v>
+      </c>
+      <c r="B20" t="s">
+        <v>513</v>
+      </c>
+      <c r="C20" t="s">
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -5067,227 +5093,227 @@
   <sheetData>
     <row r="2" ht="18" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="2" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B6" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E6" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F6" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="G6" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B8" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B9" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="11" ht="15.6" spans="1:16">
       <c r="A11" s="4" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C11" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="A12" s="4" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="P14" s="5"/>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B17" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B23" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
